--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
@@ -85,24 +85,12 @@
     <t xml:space="preserve">Aysen</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11401</t>
   </si>
   <si>
     <t xml:space="preserve">Chile Chico</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">12201</t>
   </si>
   <si>
@@ -739,6 +727,12 @@
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">16205</t>
   </si>
   <si>
@@ -1366,6 +1360,12 @@
     <t xml:space="preserve">Freirina</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">1107</t>
   </si>
   <si>
@@ -2113,7 +2113,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:20</t>
+    <t xml:space="preserve">2026-09-09 20:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2689,7 +2689,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>41.45</v>
+        <v>39.05</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>16</v>
@@ -2700,10 +2700,10 @@
         <v>2018</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>24</v>
@@ -2721,7 +2721,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>39.05</v>
+        <v>37.14</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>16</v>
@@ -2753,7 +2753,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>38.08</v>
+        <v>36.41</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
@@ -2785,7 +2785,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>37.14</v>
+        <v>36.23</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2817,7 +2817,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>36.41</v>
+        <v>35.94</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2828,10 +2828,10 @@
         <v>2018</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>32</v>
@@ -2849,7 +2849,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>36.23</v>
+        <v>34</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2860,10 +2860,10 @@
         <v>2018</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>34</v>
@@ -2881,7 +2881,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>35.94</v>
+        <v>32.06</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2913,7 +2913,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>34</v>
+        <v>31.88</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2924,10 +2924,10 @@
         <v>2018</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>38</v>
@@ -2945,7 +2945,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>32.06</v>
+        <v>31.7</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2956,10 +2956,10 @@
         <v>2018</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>40</v>
@@ -2977,7 +2977,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>31.88</v>
+        <v>31.44</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -3009,7 +3009,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>31.7</v>
+        <v>31.34</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -3020,10 +3020,10 @@
         <v>2018</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>44</v>
@@ -3041,7 +3041,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>31.44</v>
+        <v>19.51</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -3052,28 +3052,28 @@
         <v>2018</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>31.34</v>
+        <v>72.46</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -3084,28 +3084,28 @@
         <v>2018</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>19.51</v>
+        <v>67.55</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -3119,25 +3119,25 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>72.46</v>
+        <v>67.22</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -3151,7 +3151,7 @@
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>55</v>
@@ -3160,16 +3160,16 @@
         <v>56</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>67.55</v>
+        <v>62.8</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -3183,7 +3183,7 @@
         <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>57</v>
@@ -3192,16 +3192,16 @@
         <v>58</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>67.22</v>
+        <v>62.24</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -3215,7 +3215,7 @@
         <v>13</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>59</v>
@@ -3224,16 +3224,16 @@
         <v>60</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>62.8</v>
+        <v>56.63</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -3244,28 +3244,28 @@
         <v>2018</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>62.24</v>
+        <v>53.46</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -3276,28 +3276,28 @@
         <v>2018</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>56.63</v>
+        <v>51.3</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -3308,28 +3308,28 @@
         <v>2018</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>53.46</v>
+        <v>50.12</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3340,28 +3340,28 @@
         <v>2018</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>51.3</v>
+        <v>49.89</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3372,10 +3372,10 @@
         <v>2018</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3384,16 +3384,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>50.12</v>
+        <v>49.06</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3407,7 +3407,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3416,16 +3416,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>49.89</v>
+        <v>48.64</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3439,7 +3439,7 @@
         <v>13</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3448,16 +3448,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>49.06</v>
+        <v>48.43</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3471,7 +3471,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3480,16 +3480,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>48.64</v>
+        <v>46.99</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3500,10 +3500,10 @@
         <v>2018</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3512,16 +3512,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>48.43</v>
+        <v>46.95</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3535,7 +3535,7 @@
         <v>5</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3544,16 +3544,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>46.99</v>
+        <v>46.78</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3564,28 +3564,28 @@
         <v>2018</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>46.95</v>
+        <v>46.76</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3596,28 +3596,28 @@
         <v>2018</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>46.78</v>
+        <v>46.51</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3628,10 +3628,10 @@
         <v>2018</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>89</v>
@@ -3640,16 +3640,16 @@
         <v>90</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>46.76</v>
+        <v>46.42</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3660,10 +3660,10 @@
         <v>2018</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>91</v>
@@ -3672,16 +3672,16 @@
         <v>92</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46.51</v>
+        <v>46.24</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3695,7 +3695,7 @@
         <v>13</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>93</v>
@@ -3704,16 +3704,16 @@
         <v>94</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>46.42</v>
+        <v>45.71</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3724,10 +3724,10 @@
         <v>2018</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>95</v>
@@ -3736,16 +3736,16 @@
         <v>96</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>46.24</v>
+        <v>44.92</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3759,7 +3759,7 @@
         <v>13</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>97</v>
@@ -3768,16 +3768,16 @@
         <v>98</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45.71</v>
+        <v>44.09</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3788,10 +3788,10 @@
         <v>2018</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>99</v>
@@ -3800,16 +3800,16 @@
         <v>100</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>44.92</v>
+        <v>44.08</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3820,10 +3820,10 @@
         <v>2018</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>101</v>
@@ -3832,16 +3832,16 @@
         <v>102</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>44.09</v>
+        <v>44.06</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3852,10 +3852,10 @@
         <v>2018</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>103</v>
@@ -3864,16 +3864,16 @@
         <v>104</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>44.08</v>
+        <v>43.97</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3884,10 +3884,10 @@
         <v>2018</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>105</v>
@@ -3896,16 +3896,16 @@
         <v>106</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>44.06</v>
+        <v>43.69</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3916,10 +3916,10 @@
         <v>2018</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>107</v>
@@ -3928,16 +3928,16 @@
         <v>108</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>43.97</v>
+        <v>43.67</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3948,10 +3948,10 @@
         <v>2018</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>109</v>
@@ -3960,16 +3960,16 @@
         <v>110</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>43.69</v>
+        <v>43.33</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3980,10 +3980,10 @@
         <v>2018</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>111</v>
@@ -3992,16 +3992,16 @@
         <v>112</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>43.67</v>
+        <v>43.13</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -4015,7 +4015,7 @@
         <v>13</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>113</v>
@@ -4024,16 +4024,16 @@
         <v>114</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>43.33</v>
+        <v>42.92</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -4044,10 +4044,10 @@
         <v>2018</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>115</v>
@@ -4056,16 +4056,16 @@
         <v>116</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>43.13</v>
+        <v>42.52</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -4076,10 +4076,10 @@
         <v>2018</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>117</v>
@@ -4088,16 +4088,16 @@
         <v>118</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>42.92</v>
+        <v>42.28</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -4108,10 +4108,10 @@
         <v>2018</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>119</v>
@@ -4120,16 +4120,16 @@
         <v>120</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>42.52</v>
+        <v>42.27</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -4140,10 +4140,10 @@
         <v>2018</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>121</v>
@@ -4152,16 +4152,16 @@
         <v>122</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>42.28</v>
+        <v>42.18</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -4175,7 +4175,7 @@
         <v>6</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>123</v>
@@ -4184,16 +4184,16 @@
         <v>124</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>42.27</v>
+        <v>42.08</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -4204,10 +4204,10 @@
         <v>2018</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>125</v>
@@ -4216,16 +4216,16 @@
         <v>126</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>42.18</v>
+        <v>41.95</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -4236,10 +4236,10 @@
         <v>2018</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>127</v>
@@ -4248,16 +4248,16 @@
         <v>128</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>42.08</v>
+        <v>41.94</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -4268,10 +4268,10 @@
         <v>2018</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>129</v>
@@ -4280,16 +4280,16 @@
         <v>130</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>41.95</v>
+        <v>41.83</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -4300,10 +4300,10 @@
         <v>2018</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>131</v>
@@ -4312,16 +4312,16 @@
         <v>132</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>41.94</v>
+        <v>41.56</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4332,10 +4332,10 @@
         <v>2018</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>133</v>
@@ -4344,16 +4344,16 @@
         <v>134</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>41.83</v>
+        <v>41.08</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>16</v>
@@ -4364,10 +4364,10 @@
         <v>2018</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>135</v>
@@ -4376,16 +4376,16 @@
         <v>136</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>41.56</v>
+        <v>41.06</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4396,10 +4396,10 @@
         <v>2018</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>137</v>
@@ -4408,16 +4408,16 @@
         <v>138</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>41.08</v>
+        <v>41.06</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4428,10 +4428,10 @@
         <v>2018</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>139</v>
@@ -4440,16 +4440,16 @@
         <v>140</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>41.06</v>
+        <v>40.84</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4460,10 +4460,10 @@
         <v>2018</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>141</v>
@@ -4472,16 +4472,16 @@
         <v>142</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>41.06</v>
+        <v>40.79</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4492,10 +4492,10 @@
         <v>2018</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>143</v>
@@ -4504,16 +4504,16 @@
         <v>144</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>40.84</v>
+        <v>40.72</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4524,10 +4524,10 @@
         <v>2018</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>145</v>
@@ -4536,16 +4536,16 @@
         <v>146</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>40.79</v>
+        <v>40.7</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4556,10 +4556,10 @@
         <v>2018</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>147</v>
@@ -4568,16 +4568,16 @@
         <v>148</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>40.72</v>
+        <v>40.69</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4588,10 +4588,10 @@
         <v>2018</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>149</v>
@@ -4600,16 +4600,16 @@
         <v>150</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>40.7</v>
+        <v>40.55</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4620,10 +4620,10 @@
         <v>2018</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>88</v>
+        <v>61</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>151</v>
@@ -4632,16 +4632,16 @@
         <v>152</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>40.69</v>
+        <v>40.33</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4652,10 +4652,10 @@
         <v>2018</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>153</v>
@@ -4664,16 +4664,16 @@
         <v>154</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>40.55</v>
+        <v>40.3</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4684,10 +4684,10 @@
         <v>2018</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>155</v>
@@ -4696,16 +4696,16 @@
         <v>156</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>40.33</v>
+        <v>40.26</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4716,10 +4716,10 @@
         <v>2018</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>157</v>
@@ -4728,16 +4728,16 @@
         <v>158</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>40.3</v>
+        <v>40.23</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4748,10 +4748,10 @@
         <v>2018</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>159</v>
@@ -4760,16 +4760,16 @@
         <v>160</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>40.26</v>
+        <v>40.16</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4780,10 +4780,10 @@
         <v>2018</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>161</v>
@@ -4792,16 +4792,16 @@
         <v>162</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>40.23</v>
+        <v>40.14</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4812,10 +4812,10 @@
         <v>2018</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>163</v>
@@ -4824,16 +4824,16 @@
         <v>164</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>40.16</v>
+        <v>40.06</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4844,10 +4844,10 @@
         <v>2018</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>165</v>
@@ -4856,16 +4856,16 @@
         <v>166</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>40.14</v>
+        <v>39.97</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4876,10 +4876,10 @@
         <v>2018</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>167</v>
@@ -4888,16 +4888,16 @@
         <v>168</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>40.06</v>
+        <v>39.91</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4908,10 +4908,10 @@
         <v>2018</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>169</v>
@@ -4920,16 +4920,16 @@
         <v>170</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>39.97</v>
+        <v>39.78</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>16</v>
@@ -4943,7 +4943,7 @@
         <v>13</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>171</v>
@@ -4952,16 +4952,16 @@
         <v>172</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>39.91</v>
+        <v>39.7</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4972,10 +4972,10 @@
         <v>2018</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>173</v>
@@ -4984,16 +4984,16 @@
         <v>174</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>39.78</v>
+        <v>39.7</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -5007,7 +5007,7 @@
         <v>13</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>175</v>
@@ -5016,16 +5016,16 @@
         <v>176</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>39.7</v>
+        <v>39.42</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -5039,7 +5039,7 @@
         <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>177</v>
@@ -5048,16 +5048,16 @@
         <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>39.7</v>
+        <v>39.29</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -5068,10 +5068,10 @@
         <v>2018</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>179</v>
@@ -5080,16 +5080,16 @@
         <v>180</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>39.42</v>
+        <v>39.22</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -5100,10 +5100,10 @@
         <v>2018</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>181</v>
@@ -5112,16 +5112,16 @@
         <v>182</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>39.29</v>
+        <v>39.16</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -5132,10 +5132,10 @@
         <v>2018</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>183</v>
@@ -5144,16 +5144,16 @@
         <v>184</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>39.22</v>
+        <v>39</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -5167,7 +5167,7 @@
         <v>5</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>185</v>
@@ -5176,16 +5176,16 @@
         <v>186</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>39.16</v>
+        <v>38.91</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -5199,7 +5199,7 @@
         <v>5</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>187</v>
@@ -5208,16 +5208,16 @@
         <v>188</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>39</v>
+        <v>38.85</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -5228,10 +5228,10 @@
         <v>2018</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>189</v>
@@ -5240,16 +5240,16 @@
         <v>190</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>38.91</v>
+        <v>38.76</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -5263,7 +5263,7 @@
         <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>191</v>
@@ -5272,16 +5272,16 @@
         <v>192</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>38.85</v>
+        <v>38.75</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -5295,7 +5295,7 @@
         <v>6</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>193</v>
@@ -5304,16 +5304,16 @@
         <v>194</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>38.76</v>
+        <v>38.69</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5327,7 +5327,7 @@
         <v>5</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>195</v>
@@ -5336,16 +5336,16 @@
         <v>196</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>38.75</v>
+        <v>38.51</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5356,10 +5356,10 @@
         <v>2018</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>197</v>
@@ -5368,16 +5368,16 @@
         <v>198</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>38.69</v>
+        <v>38.51</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5388,10 +5388,10 @@
         <v>2018</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>199</v>
@@ -5400,16 +5400,16 @@
         <v>200</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>38.51</v>
+        <v>38.44</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5420,10 +5420,10 @@
         <v>2018</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>201</v>
@@ -5432,16 +5432,16 @@
         <v>202</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>38.51</v>
+        <v>38.4</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5452,10 +5452,10 @@
         <v>2018</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>203</v>
@@ -5464,16 +5464,16 @@
         <v>204</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>38.44</v>
+        <v>38.27</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5487,7 +5487,7 @@
         <v>6</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>205</v>
@@ -5496,16 +5496,16 @@
         <v>206</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>38.4</v>
+        <v>38.08</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5516,10 +5516,10 @@
         <v>2018</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>207</v>
@@ -5528,16 +5528,16 @@
         <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>38.27</v>
+        <v>38.03</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5548,10 +5548,10 @@
         <v>2018</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>209</v>
@@ -5560,16 +5560,16 @@
         <v>210</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>38.08</v>
+        <v>38</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5580,10 +5580,10 @@
         <v>2018</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>211</v>
@@ -5592,16 +5592,16 @@
         <v>212</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>38.03</v>
+        <v>38</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5612,28 +5612,28 @@
         <v>2018</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>213</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>214</v>
+        <v>67</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>38</v>
+        <v>37.97</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5644,28 +5644,28 @@
         <v>2018</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>216</v>
-      </c>
       <c r="F98" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5676,28 +5676,28 @@
         <v>2018</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F99" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>37.97</v>
+        <v>37.88</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5708,10 +5708,10 @@
         <v>2018</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>218</v>
@@ -5720,16 +5720,16 @@
         <v>219</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>37.9</v>
+        <v>37.86</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5743,7 +5743,7 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>220</v>
@@ -5752,16 +5752,16 @@
         <v>221</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>37.88</v>
+        <v>37.85</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5772,10 +5772,10 @@
         <v>2018</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>222</v>
@@ -5784,16 +5784,16 @@
         <v>223</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>37.86</v>
+        <v>37.81</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5807,7 +5807,7 @@
         <v>5</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>224</v>
@@ -5816,16 +5816,16 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>37.85</v>
+        <v>37.73</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5836,10 +5836,10 @@
         <v>2018</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>226</v>
@@ -5848,16 +5848,16 @@
         <v>227</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>37.81</v>
+        <v>37.54</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5871,7 +5871,7 @@
         <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>228</v>
@@ -5880,16 +5880,16 @@
         <v>229</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>37.73</v>
+        <v>37.53</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5900,10 +5900,10 @@
         <v>2018</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>230</v>
@@ -5912,16 +5912,16 @@
         <v>231</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>37.54</v>
+        <v>37.48</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5932,10 +5932,10 @@
         <v>2018</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>232</v>
@@ -5944,16 +5944,16 @@
         <v>233</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>37.53</v>
+        <v>37.45</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5964,10 +5964,10 @@
         <v>2018</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>234</v>
@@ -5976,16 +5976,16 @@
         <v>235</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>37.48</v>
+        <v>37.37</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5999,7 +5999,7 @@
         <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>236</v>
@@ -6008,16 +6008,16 @@
         <v>237</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>37.45</v>
+        <v>37.35</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>16</v>
@@ -6031,7 +6031,7 @@
         <v>16</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>238</v>
@@ -6040,16 +6040,16 @@
         <v>239</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>37.37</v>
+        <v>37.27</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -6060,10 +6060,10 @@
         <v>2018</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>240</v>
@@ -6072,16 +6072,16 @@
         <v>241</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>37.27</v>
+        <v>37.21</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>16</v>
@@ -6095,7 +6095,7 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>242</v>
@@ -6104,16 +6104,16 @@
         <v>243</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>37.21</v>
+        <v>37.16</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -6124,10 +6124,10 @@
         <v>2018</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>244</v>
@@ -6136,16 +6136,16 @@
         <v>245</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>37.16</v>
+        <v>37.15</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -6156,10 +6156,10 @@
         <v>2018</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>246</v>
@@ -6168,16 +6168,16 @@
         <v>247</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>37.15</v>
+        <v>37.14</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -6188,10 +6188,10 @@
         <v>2018</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>248</v>
@@ -6200,16 +6200,16 @@
         <v>249</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>37.14</v>
+        <v>36.99</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -6220,10 +6220,10 @@
         <v>2018</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>250</v>
@@ -6232,16 +6232,16 @@
         <v>251</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>36.99</v>
+        <v>36.91</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -6252,10 +6252,10 @@
         <v>2018</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>252</v>
@@ -6264,16 +6264,16 @@
         <v>253</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>36.91</v>
+        <v>36.8</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -6284,10 +6284,10 @@
         <v>2018</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>254</v>
@@ -6296,16 +6296,16 @@
         <v>255</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>36.8</v>
+        <v>36.72</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -6316,10 +6316,10 @@
         <v>2018</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>256</v>
@@ -6328,16 +6328,16 @@
         <v>257</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>36.72</v>
+        <v>36.52</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6351,7 +6351,7 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>258</v>
@@ -6360,16 +6360,16 @@
         <v>259</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>36.52</v>
+        <v>36.47</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6380,10 +6380,10 @@
         <v>2018</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>260</v>
@@ -6392,16 +6392,16 @@
         <v>261</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>36.47</v>
+        <v>36.43</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6412,10 +6412,10 @@
         <v>2018</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>262</v>
@@ -6424,16 +6424,16 @@
         <v>263</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>36.43</v>
+        <v>36.24</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6447,7 +6447,7 @@
         <v>13</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>264</v>
@@ -6456,16 +6456,16 @@
         <v>265</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>36.24</v>
+        <v>36.16</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6476,10 +6476,10 @@
         <v>2018</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>266</v>
@@ -6488,16 +6488,16 @@
         <v>267</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>36.16</v>
+        <v>36.14</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6508,10 +6508,10 @@
         <v>2018</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>268</v>
@@ -6520,16 +6520,16 @@
         <v>269</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>36.14</v>
+        <v>36.06</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6540,10 +6540,10 @@
         <v>2018</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>270</v>
@@ -6552,16 +6552,16 @@
         <v>271</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>36.06</v>
+        <v>35.97</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6572,10 +6572,10 @@
         <v>2018</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>272</v>
@@ -6584,16 +6584,16 @@
         <v>273</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>35.97</v>
+        <v>35.96</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6607,7 +6607,7 @@
         <v>16</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>274</v>
@@ -6616,16 +6616,16 @@
         <v>275</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>35.96</v>
+        <v>35.92</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6636,10 +6636,10 @@
         <v>2018</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>276</v>
@@ -6648,16 +6648,16 @@
         <v>277</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>35.92</v>
+        <v>35.79</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6668,10 +6668,10 @@
         <v>2018</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>278</v>
@@ -6680,16 +6680,16 @@
         <v>279</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>35.79</v>
+        <v>35.68</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6700,10 +6700,10 @@
         <v>2018</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>280</v>
@@ -6712,16 +6712,16 @@
         <v>281</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>35.68</v>
+        <v>35.59</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6732,10 +6732,10 @@
         <v>2018</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>282</v>
@@ -6744,16 +6744,16 @@
         <v>283</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>35.59</v>
+        <v>35.58</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6764,10 +6764,10 @@
         <v>2018</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>284</v>
@@ -6776,16 +6776,16 @@
         <v>285</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>35.58</v>
+        <v>35.54</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6796,10 +6796,10 @@
         <v>2018</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>286</v>
@@ -6808,16 +6808,16 @@
         <v>287</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>35.54</v>
+        <v>35.44</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6828,10 +6828,10 @@
         <v>2018</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>288</v>
@@ -6840,16 +6840,16 @@
         <v>289</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>35.44</v>
+        <v>35.41</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6860,10 +6860,10 @@
         <v>2018</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>290</v>
@@ -6872,16 +6872,16 @@
         <v>291</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>35.41</v>
+        <v>35.4</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6895,7 +6895,7 @@
         <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>292</v>
@@ -6904,16 +6904,16 @@
         <v>293</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>35.4</v>
+        <v>35.39</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6924,10 +6924,10 @@
         <v>2018</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>294</v>
@@ -6936,16 +6936,16 @@
         <v>295</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>35.39</v>
+        <v>35.38</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6959,7 +6959,7 @@
         <v>6</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>296</v>
@@ -6968,16 +6968,16 @@
         <v>297</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>35.38</v>
+        <v>35.32</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6988,10 +6988,10 @@
         <v>2018</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>298</v>
@@ -7000,16 +7000,16 @@
         <v>299</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>35.32</v>
+        <v>35.21</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -7020,10 +7020,10 @@
         <v>2018</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>300</v>
@@ -7032,16 +7032,16 @@
         <v>301</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>35.21</v>
+        <v>35.16</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -7052,10 +7052,10 @@
         <v>2018</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>302</v>
@@ -7064,16 +7064,16 @@
         <v>303</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>35.16</v>
+        <v>35.09</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -7084,10 +7084,10 @@
         <v>2018</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>304</v>
@@ -7096,16 +7096,16 @@
         <v>305</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>35.09</v>
+        <v>35.01</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -7119,7 +7119,7 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>306</v>
@@ -7128,16 +7128,16 @@
         <v>307</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>35.01</v>
+        <v>34.88</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -7148,10 +7148,10 @@
         <v>2018</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>308</v>
@@ -7160,16 +7160,16 @@
         <v>309</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>34.88</v>
+        <v>34.85</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -7180,10 +7180,10 @@
         <v>2018</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>310</v>
@@ -7192,16 +7192,16 @@
         <v>311</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>34.85</v>
+        <v>34.81</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -7212,10 +7212,10 @@
         <v>2018</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>312</v>
@@ -7224,16 +7224,16 @@
         <v>313</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>34.81</v>
+        <v>34.67</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -7244,10 +7244,10 @@
         <v>2018</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>314</v>
@@ -7256,16 +7256,16 @@
         <v>315</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>34.67</v>
+        <v>34.48</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -7276,10 +7276,10 @@
         <v>2018</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>316</v>
@@ -7288,16 +7288,16 @@
         <v>317</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>34.48</v>
+        <v>34.32</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -7308,10 +7308,10 @@
         <v>2018</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>318</v>
@@ -7320,16 +7320,16 @@
         <v>319</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>34.32</v>
+        <v>34.3</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>320</v>
@@ -7352,16 +7352,16 @@
         <v>321</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>34.3</v>
+        <v>34.11</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7375,7 +7375,7 @@
         <v>7</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>322</v>
@@ -7384,16 +7384,16 @@
         <v>323</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>34.11</v>
+        <v>34.09</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7407,7 +7407,7 @@
         <v>7</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>324</v>
@@ -7416,16 +7416,16 @@
         <v>325</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>34.09</v>
+        <v>33.92</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7439,7 +7439,7 @@
         <v>7</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>326</v>
@@ -7448,16 +7448,16 @@
         <v>327</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>33.92</v>
+        <v>33.8</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7468,10 +7468,10 @@
         <v>2018</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>328</v>
@@ -7480,16 +7480,16 @@
         <v>329</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>33.8</v>
+        <v>33.78</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7500,10 +7500,10 @@
         <v>2018</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>330</v>
@@ -7512,16 +7512,16 @@
         <v>331</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>33.78</v>
+        <v>33.76</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7532,10 +7532,10 @@
         <v>2018</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>332</v>
@@ -7544,16 +7544,16 @@
         <v>333</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>33.76</v>
+        <v>33.7</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7567,7 +7567,7 @@
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>334</v>
@@ -7576,16 +7576,16 @@
         <v>335</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>33.7</v>
+        <v>33.52</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>16</v>
@@ -7599,7 +7599,7 @@
         <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>336</v>
@@ -7608,16 +7608,16 @@
         <v>337</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>33.52</v>
+        <v>33.44</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>16</v>
@@ -7628,10 +7628,10 @@
         <v>2018</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>338</v>
@@ -7640,16 +7640,16 @@
         <v>339</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>33.44</v>
+        <v>33.42</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>16</v>
@@ -7660,10 +7660,10 @@
         <v>2018</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>88</v>
+        <v>64</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>340</v>
@@ -7672,16 +7672,16 @@
         <v>341</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>33.42</v>
+        <v>33.37</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>16</v>
@@ -7692,10 +7692,10 @@
         <v>2018</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>342</v>
@@ -7704,16 +7704,16 @@
         <v>343</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>33.37</v>
+        <v>33.34</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>16</v>
@@ -7724,10 +7724,10 @@
         <v>2018</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>344</v>
@@ -7736,16 +7736,16 @@
         <v>345</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>33.34</v>
+        <v>33.33</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>16</v>
@@ -7756,10 +7756,10 @@
         <v>2018</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>346</v>
@@ -7768,16 +7768,16 @@
         <v>347</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>33.33</v>
+        <v>33.23</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>16</v>
@@ -7788,10 +7788,10 @@
         <v>2018</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>348</v>
@@ -7800,16 +7800,16 @@
         <v>349</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>33.23</v>
+        <v>33.19</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>16</v>
@@ -7820,10 +7820,10 @@
         <v>2018</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>350</v>
@@ -7832,16 +7832,16 @@
         <v>351</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>33.19</v>
+        <v>33.07</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>16</v>
@@ -7852,10 +7852,10 @@
         <v>2018</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>65</v>
+        <v>84</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>352</v>
@@ -7864,16 +7864,16 @@
         <v>353</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>33.07</v>
+        <v>32.9</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>16</v>
@@ -7884,10 +7884,10 @@
         <v>2018</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>88</v>
+        <v>46</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>354</v>
@@ -7896,16 +7896,16 @@
         <v>355</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>32.9</v>
+        <v>32.87</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>16</v>
@@ -7916,10 +7916,10 @@
         <v>2018</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>356</v>
@@ -7928,16 +7928,16 @@
         <v>357</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>32.87</v>
+        <v>32.84</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>16</v>
@@ -7948,10 +7948,10 @@
         <v>2018</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>358</v>
@@ -7960,16 +7960,16 @@
         <v>359</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>32.84</v>
+        <v>32.81</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>16</v>
@@ -7980,10 +7980,10 @@
         <v>2018</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>360</v>
@@ -7992,16 +7992,16 @@
         <v>361</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>32.81</v>
+        <v>32.75</v>
       </c>
       <c r="J171" s="2" t="s">
         <v>16</v>
@@ -8012,10 +8012,10 @@
         <v>2018</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>362</v>
@@ -8024,16 +8024,16 @@
         <v>363</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>32.75</v>
+        <v>32.51</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>16</v>
@@ -8044,10 +8044,10 @@
         <v>2018</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>364</v>
@@ -8056,16 +8056,16 @@
         <v>365</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>32.51</v>
+        <v>32.16</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>16</v>
@@ -8076,10 +8076,10 @@
         <v>2018</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>366</v>
@@ -8088,16 +8088,16 @@
         <v>367</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>32.16</v>
+        <v>32.13</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>16</v>
@@ -8108,10 +8108,10 @@
         <v>2018</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>368</v>
@@ -8120,16 +8120,16 @@
         <v>369</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>32.13</v>
+        <v>32.09</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>16</v>
@@ -8143,7 +8143,7 @@
         <v>16</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>370</v>
@@ -8152,16 +8152,16 @@
         <v>371</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>32.09</v>
+        <v>31.79</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>16</v>
@@ -8175,7 +8175,7 @@
         <v>16</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>372</v>
@@ -8184,16 +8184,16 @@
         <v>373</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>31.79</v>
+        <v>31.66</v>
       </c>
       <c r="J177" s="2" t="s">
         <v>16</v>
@@ -8204,10 +8204,10 @@
         <v>2018</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>374</v>
@@ -8216,16 +8216,16 @@
         <v>375</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>31.66</v>
+        <v>31.47</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>16</v>
@@ -8236,10 +8236,10 @@
         <v>2018</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>376</v>
@@ -8248,16 +8248,16 @@
         <v>377</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>31.47</v>
+        <v>31.13</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>16</v>
@@ -8268,10 +8268,10 @@
         <v>2018</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>378</v>
@@ -8280,16 +8280,16 @@
         <v>379</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>31.13</v>
+        <v>30.89</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>16</v>
@@ -8303,7 +8303,7 @@
         <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>380</v>
@@ -8312,16 +8312,16 @@
         <v>381</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>30.89</v>
+        <v>30.03</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>16</v>
@@ -8335,7 +8335,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>382</v>
@@ -8344,16 +8344,16 @@
         <v>383</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>30.03</v>
+        <v>29.56</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>16</v>
@@ -8367,7 +8367,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>384</v>
@@ -8376,16 +8376,16 @@
         <v>385</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>29.56</v>
+        <v>29.49</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>16</v>
@@ -8396,10 +8396,10 @@
         <v>2018</v>
       </c>
       <c r="B184" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>386</v>
@@ -8408,16 +8408,16 @@
         <v>387</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>29.49</v>
+        <v>29.11</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>16</v>
@@ -8428,10 +8428,10 @@
         <v>2018</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D185" s="2" t="s">
         <v>388</v>
@@ -8440,16 +8440,16 @@
         <v>389</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>29.11</v>
+        <v>29.08</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>16</v>
@@ -8460,10 +8460,10 @@
         <v>2018</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>390</v>
@@ -8472,16 +8472,16 @@
         <v>391</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>29.08</v>
+        <v>28.73</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>16</v>
@@ -8492,10 +8492,10 @@
         <v>2018</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>71</v>
+        <v>46</v>
       </c>
       <c r="D187" s="2" t="s">
         <v>392</v>
@@ -8504,16 +8504,16 @@
         <v>393</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>28.73</v>
+        <v>25.95</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>16</v>
@@ -8524,28 +8524,28 @@
         <v>2018</v>
       </c>
       <c r="B188" s="2" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>50</v>
+        <v>394</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>53</v>
+        <v>397</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>54</v>
+        <v>398</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>25.95</v>
+        <v>46.89</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>16</v>
@@ -8556,28 +8556,28 @@
         <v>2018</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="D189" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="F189" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="E189" s="2" t="s">
+      <c r="G189" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="F189" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="G189" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>46.89</v>
+        <v>43.98</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>16</v>
@@ -8588,28 +8588,28 @@
         <v>2018</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>402</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>43.98</v>
+        <v>43.09</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>16</v>
@@ -8620,28 +8620,28 @@
         <v>2018</v>
       </c>
       <c r="B191" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>404</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>43.09</v>
+        <v>41.85</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>16</v>
@@ -8652,10 +8652,10 @@
         <v>2018</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>406</v>
@@ -8664,16 +8664,16 @@
         <v>407</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>41.85</v>
+        <v>41.38</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>16</v>
@@ -8684,28 +8684,28 @@
         <v>2018</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>41.38</v>
+        <v>41.36</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>16</v>
@@ -8716,28 +8716,28 @@
         <v>2018</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E194" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="F194" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>41.36</v>
+        <v>40.7</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>16</v>
@@ -8748,28 +8748,28 @@
         <v>2018</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C195" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D195" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D195" s="2" t="s">
+      <c r="E195" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="E195" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="F195" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>40.7</v>
+        <v>40.17</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>16</v>
@@ -8780,10 +8780,10 @@
         <v>2018</v>
       </c>
       <c r="B196" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>415</v>
@@ -8792,16 +8792,16 @@
         <v>416</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>40.17</v>
+        <v>39.85</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>16</v>
@@ -8812,10 +8812,10 @@
         <v>2018</v>
       </c>
       <c r="B197" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>417</v>
@@ -8824,16 +8824,16 @@
         <v>418</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>39.85</v>
+        <v>39.56</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>16</v>
@@ -8844,10 +8844,10 @@
         <v>2018</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D198" s="2" t="s">
         <v>419</v>
@@ -8856,16 +8856,16 @@
         <v>420</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>39.56</v>
+        <v>39.44</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>16</v>
@@ -8876,10 +8876,10 @@
         <v>2018</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>421</v>
@@ -8888,16 +8888,16 @@
         <v>422</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>39.44</v>
+        <v>37.89</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>16</v>
@@ -8908,10 +8908,10 @@
         <v>2018</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>423</v>
@@ -8920,16 +8920,16 @@
         <v>424</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>37.89</v>
+        <v>37.62</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>16</v>
@@ -8943,7 +8943,7 @@
         <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>425</v>
@@ -8952,16 +8952,16 @@
         <v>426</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>37.62</v>
+        <v>37.41</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>16</v>
@@ -8972,10 +8972,10 @@
         <v>2018</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>427</v>
@@ -8984,16 +8984,16 @@
         <v>428</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>37.41</v>
+        <v>37.18</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>16</v>
@@ -9004,10 +9004,10 @@
         <v>2018</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>429</v>
@@ -9016,16 +9016,16 @@
         <v>430</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>37.18</v>
+        <v>36.01</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>16</v>
@@ -9039,7 +9039,7 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>431</v>
@@ -9048,16 +9048,16 @@
         <v>432</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>36.01</v>
+        <v>35.72</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>16</v>
@@ -9068,10 +9068,10 @@
         <v>2018</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>396</v>
+        <v>411</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>433</v>
@@ -9080,16 +9080,16 @@
         <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>35.72</v>
+        <v>35.56</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>16</v>
@@ -9100,10 +9100,10 @@
         <v>2018</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9112,16 +9112,16 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>35.56</v>
+        <v>34.98</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>16</v>
@@ -9132,10 +9132,10 @@
         <v>2018</v>
       </c>
       <c r="B207" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
@@ -9144,16 +9144,16 @@
         <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>34.98</v>
+        <v>34.64</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>16</v>
@@ -9164,10 +9164,10 @@
         <v>2018</v>
       </c>
       <c r="B208" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>439</v>
@@ -9176,16 +9176,16 @@
         <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>34.64</v>
+        <v>33.97</v>
       </c>
       <c r="J208" s="2" t="s">
         <v>16</v>
@@ -9199,7 +9199,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>441</v>
@@ -9208,16 +9208,16 @@
         <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>33.97</v>
+        <v>33.75</v>
       </c>
       <c r="J209" s="2" t="s">
         <v>16</v>
@@ -9231,7 +9231,7 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>443</v>
@@ -9240,16 +9240,16 @@
         <v>444</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>33.75</v>
+        <v>32.96</v>
       </c>
       <c r="J210" s="2" t="s">
         <v>16</v>
@@ -9260,10 +9260,10 @@
         <v>2018</v>
       </c>
       <c r="B211" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>445</v>
@@ -9272,16 +9272,16 @@
         <v>446</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>32.96</v>
+        <v>32.82</v>
       </c>
       <c r="J211" s="2" t="s">
         <v>16</v>
@@ -9292,10 +9292,10 @@
         <v>2018</v>
       </c>
       <c r="B212" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>410</v>
+        <v>394</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>447</v>
@@ -9304,16 +9304,16 @@
         <v>448</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>32.82</v>
+        <v>32.42</v>
       </c>
       <c r="J212" s="2" t="s">
         <v>16</v>
@@ -9327,7 +9327,7 @@
         <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>449</v>
@@ -9336,10 +9336,10 @@
         <v>450</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9359,7 +9359,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>451</v>
@@ -9368,10 +9368,10 @@
         <v>452</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9391,7 +9391,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>453</v>
@@ -9400,10 +9400,10 @@
         <v>454</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9423,7 +9423,7 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>455</v>
@@ -9432,10 +9432,10 @@
         <v>456</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9455,7 +9455,7 @@
         <v>1</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>457</v>
@@ -9464,10 +9464,10 @@
         <v>458</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9487,7 +9487,7 @@
         <v>4</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>459</v>
@@ -9496,10 +9496,10 @@
         <v>460</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9519,7 +9519,7 @@
         <v>3</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>461</v>
@@ -9528,10 +9528,10 @@
         <v>462</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9551,7 +9551,7 @@
         <v>2</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>463</v>
@@ -9560,10 +9560,10 @@
         <v>464</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9583,7 +9583,7 @@
         <v>1</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>465</v>
@@ -9592,10 +9592,10 @@
         <v>466</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9615,7 +9615,7 @@
         <v>2</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>467</v>
@@ -9624,10 +9624,10 @@
         <v>468</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9647,7 +9647,7 @@
         <v>3</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>469</v>
@@ -9656,10 +9656,10 @@
         <v>470</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9679,7 +9679,7 @@
         <v>2</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>471</v>
@@ -9688,10 +9688,10 @@
         <v>472</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9711,7 +9711,7 @@
         <v>1</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>473</v>
@@ -9720,10 +9720,10 @@
         <v>474</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9743,7 +9743,7 @@
         <v>2</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D226" s="2" t="s">
         <v>475</v>
@@ -9752,10 +9752,10 @@
         <v>476</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9775,7 +9775,7 @@
         <v>4</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>477</v>
@@ -9784,10 +9784,10 @@
         <v>478</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
@@ -2113,7 +2113,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:05</t>
+    <t xml:space="preserve">2026-09-18 11:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2018.xlsx
@@ -2113,7 +2113,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:27</t>
+    <t xml:space="preserve">2026-09-24 00:19</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
